--- a/HSI_FSC_0_basic/result/score_basic.xlsx
+++ b/HSI_FSC_0_basic/result/score_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_0_basic\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB67040E-6A37-45EA-BAE8-2BF07ADA3726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE9C04C-9E05-4FD9-B312-EEFE44D06022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="1920" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="1170" windowWidth="21600" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,32 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>XZ</t>
+  </si>
+  <si>
+    <t>OA(%)</t>
+  </si>
+  <si>
+    <t>AA(%)</t>
+  </si>
+  <si>
+    <t>KAPPA(*100)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -364,10 +390,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>40</v>
       </c>
@@ -406,7 +435,7 @@
         <v>31.844011909090909</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>44.220730000000003</v>
       </c>
@@ -444,8 +473,20 @@
         <f t="shared" ref="L2:L19" si="0">AVERAGE(A2:K2)</f>
         <v>46.36256854545455</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>31.520223999999999</v>
       </c>
@@ -483,8 +524,24 @@
         <f t="shared" si="0"/>
         <v>34.417541454545464</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3">
+        <v>58.581325007317702</v>
+      </c>
+      <c r="Q3" s="1">
+        <f t="shared" ref="Q3:Q5" si="1">AVERAGE(F3:P3)</f>
+        <v>35.319704932732897</v>
+      </c>
+      <c r="R3">
+        <v>78.7871703759117</v>
+      </c>
+      <c r="S3" s="2">
+        <v>84.161621441119607</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>69.938643999999996</v>
       </c>
@@ -522,8 +579,24 @@
         <f t="shared" si="0"/>
         <v>38.353631999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O4" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>57.600200176238999</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="1"/>
+        <v>35.360522022029876</v>
+      </c>
+      <c r="R4">
+        <v>74.969553947448702</v>
+      </c>
+      <c r="S4" s="2">
+        <v>79.422736167907701</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>60.224716000000001</v>
       </c>
@@ -561,8 +634,24 @@
         <f t="shared" si="0"/>
         <v>57.427013454545452</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5">
+        <v>53.984732202108297</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="1"/>
+        <v>52.76684045708172</v>
+      </c>
+      <c r="R5">
+        <v>71.936903318411495</v>
+      </c>
+      <c r="S5" s="2">
+        <v>79.685225351475097</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>95.409180000000006</v>
       </c>
@@ -601,7 +690,7 @@
         <v>94.409387818181827</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8.6687309999999993</v>
       </c>
@@ -640,7 +729,7 @@
         <v>28.967268181818181</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>88.490560000000002</v>
       </c>
@@ -679,7 +768,7 @@
         <v>89.039125999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11.173183999999999</v>
       </c>
@@ -718,7 +807,7 @@
         <v>25.004091727272733</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>61.649940000000001</v>
       </c>
@@ -757,7 +846,7 @@
         <v>39.336775272727273</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>70.784030000000001</v>
       </c>
@@ -796,7 +885,7 @@
         <v>63.772725727272729</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>32.778489999999998</v>
       </c>
@@ -835,7 +924,7 @@
         <v>35.406395272727281</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>82.448975000000004</v>
       </c>
@@ -874,7 +963,7 @@
         <v>66.665082727272718</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>89.482069999999993</v>
       </c>
@@ -913,7 +1002,7 @@
         <v>89.626471818181798</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>59.203983000000001</v>
       </c>
@@ -952,7 +1041,7 @@
         <v>59.075346545454543</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>75.609759999999994</v>
       </c>
@@ -1862,6 +1951,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2638,6 +2728,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/HSI_FSC_0_basic/result/score_basic.xlsx
+++ b/HSI_FSC_0_basic/result/score_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_0_basic\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE9C04C-9E05-4FD9-B312-EEFE44D06022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E5CCD0-9C23-4227-BCC9-FFF53668A510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1170" windowWidth="21600" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -65,12 +65,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -112,7 +119,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -391,12 +398,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>40</v>
       </c>
@@ -435,7 +442,7 @@
         <v>31.844011909090909</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>44.220730000000003</v>
       </c>
@@ -486,7 +493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>31.520223999999999</v>
       </c>
@@ -541,7 +548,7 @@
         <v>84.161621441119607</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>69.938643999999996</v>
       </c>
@@ -596,7 +603,7 @@
         <v>79.422736167907701</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>60.224716000000001</v>
       </c>
@@ -651,7 +658,7 @@
         <v>79.685225351475097</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>95.409180000000006</v>
       </c>
@@ -690,7 +697,7 @@
         <v>94.409387818181827</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>8.6687309999999993</v>
       </c>
@@ -729,7 +736,7 @@
         <v>28.967268181818181</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>88.490560000000002</v>
       </c>
@@ -768,7 +775,7 @@
         <v>89.039125999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>11.173183999999999</v>
       </c>
@@ -807,7 +814,7 @@
         <v>25.004091727272733</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>61.649940000000001</v>
       </c>
@@ -846,7 +853,7 @@
         <v>39.336775272727273</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>70.784030000000001</v>
       </c>
@@ -885,7 +892,7 @@
         <v>63.772725727272729</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>32.778489999999998</v>
       </c>
@@ -924,7 +931,7 @@
         <v>35.406395272727281</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>82.448975000000004</v>
       </c>
@@ -963,7 +970,7 @@
         <v>66.665082727272718</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>89.482069999999993</v>
       </c>
@@ -1002,7 +1009,7 @@
         <v>89.626471818181798</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>59.203983000000001</v>
       </c>
@@ -1041,7 +1048,7 @@
         <v>59.075346545454543</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>75.609759999999994</v>
       </c>
@@ -1080,7 +1087,7 @@
         <v>41.755500545454545</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>58.581325007317702</v>
       </c>
@@ -1119,7 +1126,7 @@
         <v>53.724088381128041</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>57.600200176238999</v>
       </c>
@@ -1158,7 +1165,7 @@
         <v>52.591433850201632</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>53.984732202108297</v>
       </c>
@@ -1198,6 +1205,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1206,9 +1214,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>97.856800000000007</v>
       </c>
@@ -1247,7 +1255,7 @@
         <v>87.697773636363635</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>87.863590000000002</v>
       </c>
@@ -1286,7 +1294,7 @@
         <v>92.726368727272714</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>94.393424999999993</v>
       </c>
@@ -1325,7 +1333,7 @@
         <v>91.023622727272723</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>77.678569999999993</v>
       </c>
@@ -1364,7 +1372,7 @@
         <v>88.895162181818165</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>100</v>
       </c>
@@ -1403,7 +1411,7 @@
         <v>98.335348909090911</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>98.966735999999997</v>
       </c>
@@ -1442,7 +1450,7 @@
         <v>98.221042909090912</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>94.355099999999993</v>
       </c>
@@ -1481,7 +1489,7 @@
         <v>94.694745636363663</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>75.237020000000001</v>
       </c>
@@ -1520,7 +1528,7 @@
         <v>86.069763636363632</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>99.917534000000003</v>
       </c>
@@ -1559,7 +1567,7 @@
         <v>98.479192999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>88.706680000000006</v>
       </c>
@@ -1598,7 +1606,7 @@
         <v>89.503166727272728</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>80.030370000000005</v>
       </c>
@@ -1637,7 +1645,7 @@
         <v>90.498172545454537</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>99.946920000000006</v>
       </c>
@@ -1676,7 +1684,7 @@
         <v>94.660199090909089</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>100</v>
       </c>
@@ -1715,7 +1723,7 @@
         <v>95.760942181818166</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>65.177475000000001</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>80.621132090909086</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>51.552245999999997</v>
       </c>
@@ -1793,7 +1801,7 @@
         <v>64.728680727272732</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>88.151179999999997</v>
       </c>
@@ -1832,7 +1840,7 @@
         <v>94.891184999999993</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>82.220251621127304</v>
       </c>
@@ -1871,7 +1879,7 @@
         <v>86.86672746418904</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>87.489604949951101</v>
       </c>
@@ -1910,7 +1918,7 @@
         <v>90.425407344644682</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>80.331013381055499</v>
       </c>
@@ -1950,6 +1958,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1958,9 +1967,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>84.450519999999997</v>
       </c>
@@ -1999,7 +2008,7 @@
         <v>86.15640272727272</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>87.641630000000006</v>
       </c>
@@ -2038,7 +2047,7 @@
         <v>92.853303636363634</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>57.319873999999999</v>
       </c>
@@ -2077,7 +2086,7 @@
         <v>60.382887272727274</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>70.284970000000001</v>
       </c>
@@ -2116,7 +2125,7 @@
         <v>78.167175545454555</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>99.112430000000003</v>
       </c>
@@ -2155,7 +2164,7 @@
         <v>94.089795000000009</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>56.566249999999997</v>
       </c>
@@ -2194,7 +2203,7 @@
         <v>45.053858545454545</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>42.494999999999997</v>
       </c>
@@ -2233,7 +2242,7 @@
         <v>52.915048090909089</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>87.479060000000004</v>
       </c>
@@ -2272,7 +2281,7 @@
         <v>71.877165181818185</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>89.376220000000004</v>
       </c>
@@ -2311,7 +2320,7 @@
         <v>65.600855636363647</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>78.7871703759117</v>
       </c>
@@ -2350,7 +2359,7 @@
         <v>73.654300627369594</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>74.969553947448702</v>
       </c>
@@ -2389,7 +2398,7 @@
         <v>71.899610215967314</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>71.936903318411495</v>
       </c>
@@ -2429,6 +2438,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2436,9 +2446,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>96.214399999999998</v>
       </c>
@@ -2462,7 +2472,7 @@
         <v>93.298509166666648</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>88.03913</v>
       </c>
@@ -2486,7 +2496,7 @@
         <v>88.516750833333333</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>80.938649999999996</v>
       </c>
@@ -2510,7 +2520,7 @@
         <v>72.473623333333322</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>55.507052999999999</v>
       </c>
@@ -2534,7 +2544,7 @@
         <v>50.382843833333332</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>91.290350000000004</v>
       </c>
@@ -2558,7 +2568,7 @@
         <v>89.653434166666671</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>29.976469000000002</v>
       </c>
@@ -2582,7 +2592,7 @@
         <v>50.893686500000001</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>72.051190000000005</v>
       </c>
@@ -2606,7 +2616,7 @@
         <v>74.507542999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>89.202359999999999</v>
       </c>
@@ -2630,7 +2640,7 @@
         <v>87.092550166666669</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>53.418804000000002</v>
       </c>
@@ -2654,7 +2664,7 @@
         <v>62.827751999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>79.993321428052894</v>
       </c>
@@ -2678,7 +2688,7 @@
         <v>80.329669797852176</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>72.959828376770005</v>
       </c>
@@ -2702,7 +2712,7 @@
         <v>74.405190348625169</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>75.217083885347805</v>
       </c>
@@ -2727,6 +2737,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -2735,8 +2746,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>